--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD861CE-7C08-4953-B64D-6F952E74E5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C4EDA4A-6B77-C441-939E-12D1462ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="167">
   <si>
     <t>Venue</t>
   </si>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>Corrigan Park</t>
+  </si>
+  <si>
+    <t>Fontenoy Park, Liatroim Co. Down</t>
   </si>
 </sst>
 </file>
@@ -905,14 +908,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B130"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B131"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.1953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -920,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -928,7 +931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -936,7 +939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -944,7 +947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -952,7 +955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -960,7 +963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -968,7 +971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -976,7 +979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -984,7 +987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -992,7 +995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1000,7 +1003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1032,7 +1035,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1040,7 +1043,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1048,7 +1051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1072,7 +1075,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1080,7 +1083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -1104,7 +1107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1112,7 +1115,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -1144,7 +1147,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1160,7 +1163,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1280,7 +1283,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -1312,7 +1315,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -1336,7 +1339,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1344,7 +1347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1360,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -1376,7 +1379,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1384,7 +1387,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>91</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>93</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>95</v>
       </c>
@@ -1416,7 +1419,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>97</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>98</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>99</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>101</v>
       </c>
@@ -1448,7 +1451,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>102</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>103</v>
       </c>
@@ -1464,7 +1467,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>104</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -1480,7 +1483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>107</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>108</v>
       </c>
@@ -1496,7 +1499,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -1528,7 +1531,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -1536,7 +1539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -1544,7 +1547,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>115</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>116</v>
       </c>
@@ -1560,7 +1563,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>117</v>
       </c>
@@ -1568,7 +1571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>119</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -1624,7 +1627,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -1640,7 +1643,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>127</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -1656,7 +1659,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -1664,7 +1667,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>130</v>
       </c>
@@ -1672,7 +1675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>132</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -1696,7 +1699,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>134</v>
       </c>
@@ -1704,7 +1707,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -1712,7 +1715,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -1728,7 +1731,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -1736,7 +1739,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -1752,7 +1755,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -1760,7 +1763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -1768,7 +1771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>143</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>144</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>145</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>146</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>149</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -1832,7 +1835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>151</v>
       </c>
@@ -1840,7 +1843,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>152</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>154</v>
       </c>
@@ -1864,7 +1867,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>155</v>
       </c>
@@ -1872,7 +1875,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -1904,7 +1907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -1912,7 +1915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -1936,7 +1939,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -1944,12 +1947,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>165</v>
       </c>
       <c r="B130" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>166</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C4EDA4A-6B77-C441-939E-12D1462ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4CB06-95B1-45EB-80BF-A9762FD48596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
   <si>
     <t>Venue</t>
   </si>
@@ -537,6 +537,9 @@
   </si>
   <si>
     <t>Fontenoy Park, Liatroim Co. Down</t>
+  </si>
+  <si>
+    <t>Erins Own, Cargin (Toomebridge)</t>
   </si>
 </sst>
 </file>
@@ -908,14 +911,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B131"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B132"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.1953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -923,7 +926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -931,7 +934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -939,7 +942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -947,7 +950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -955,7 +958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -963,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -971,7 +974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -979,7 +982,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -987,7 +990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -995,7 +998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1003,7 +1006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1019,7 +1022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1027,7 +1030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1043,7 +1046,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1091,7 +1094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1099,7 +1102,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -1107,7 +1110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1115,7 +1118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1139,7 +1142,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -1171,7 +1174,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1179,7 +1182,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1203,7 +1206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -1227,7 +1230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -1259,7 +1262,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -1275,7 +1278,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1283,7 +1286,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1347,7 +1350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>91</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -1403,7 +1406,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>93</v>
       </c>
@@ -1411,7 +1414,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>95</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>97</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>98</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>99</v>
       </c>
@@ -1443,7 +1446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>101</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>102</v>
       </c>
@@ -1459,7 +1462,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>103</v>
       </c>
@@ -1467,7 +1470,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>104</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -1483,7 +1486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>107</v>
       </c>
@@ -1491,7 +1494,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>108</v>
       </c>
@@ -1499,7 +1502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -1547,7 +1550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>115</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>116</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>117</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -1579,7 +1582,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>119</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -1619,7 +1622,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -1643,7 +1646,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>127</v>
       </c>
@@ -1651,7 +1654,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -1659,7 +1662,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>130</v>
       </c>
@@ -1675,7 +1678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>132</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>134</v>
       </c>
@@ -1707,7 +1710,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -1731,7 +1734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -1747,7 +1750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -1755,7 +1758,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -1763,7 +1766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>143</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>144</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>145</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>146</v>
       </c>
@@ -1803,7 +1806,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>149</v>
       </c>
@@ -1827,7 +1830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -1835,7 +1838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>151</v>
       </c>
@@ -1843,7 +1846,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>152</v>
       </c>
@@ -1851,7 +1854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>154</v>
       </c>
@@ -1867,7 +1870,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>155</v>
       </c>
@@ -1875,7 +1878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -1883,7 +1886,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -1891,7 +1894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -1915,7 +1918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -1923,7 +1926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -1931,7 +1934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -1939,7 +1942,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>165</v>
       </c>
@@ -1955,12 +1958,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>166</v>
       </c>
       <c r="B131" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4CB06-95B1-45EB-80BF-A9762FD48596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{622621FF-098C-4A00-865A-37CA5BD144E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="169">
   <si>
     <t>Venue</t>
   </si>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>Erins Own, Cargin (Toomebridge)</t>
+  </si>
+  <si>
+    <t>O'Donnell Park, Letterkenny</t>
   </si>
 </sst>
 </file>
@@ -911,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -1974,6 +1977,14 @@
         <v>35</v>
       </c>
     </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>168</v>
+      </c>
+      <c r="B133" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{622621FF-098C-4A00-865A-37CA5BD144E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A304DAA0-BF46-43E0-8731-01E887665622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="172">
   <si>
     <t>Venue</t>
   </si>
@@ -543,6 +543,15 @@
   </si>
   <si>
     <t>O'Donnell Park, Letterkenny</t>
+  </si>
+  <si>
+    <t>Ballyforan</t>
+  </si>
+  <si>
+    <t>Dunloy</t>
+  </si>
+  <si>
+    <t>Patrick McManus Park, Kinawley</t>
   </si>
 </sst>
 </file>
@@ -914,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -1985,6 +1994,30 @@
         <v>9</v>
       </c>
     </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>169</v>
+      </c>
+      <c r="B134" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>170</v>
+      </c>
+      <c r="B135" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>171</v>
+      </c>
+      <c r="B136" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A304DAA0-BF46-43E0-8731-01E887665622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D031B3-273C-446A-BAA9-5C16A7C2B79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$137</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="173">
   <si>
     <t>Venue</t>
   </si>
@@ -552,6 +555,9 @@
   </si>
   <si>
     <t>Patrick McManus Park, Kinawley</t>
+  </si>
+  <si>
+    <t>Glenisk O'Connor Park, Tullamore</t>
   </si>
 </sst>
 </file>
@@ -923,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -2018,6 +2024,14 @@
         <v>18</v>
       </c>
     </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>172</v>
+      </c>
+      <c r="B137" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D031B3-273C-446A-BAA9-5C16A7C2B79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4561D1F-F240-414F-9B69-C0666E77BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="174">
   <si>
     <t>Venue</t>
   </si>
@@ -558,6 +558,9 @@
   </si>
   <si>
     <t>Glenisk O'Connor Park, Tullamore</t>
+  </si>
+  <si>
+    <t>Netwatch Cullen Park, Carlow</t>
   </si>
 </sst>
 </file>
@@ -929,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B137"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -2032,6 +2035,14 @@
         <v>51</v>
       </c>
     </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>173</v>
+      </c>
+      <c r="B138" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4561D1F-F240-414F-9B69-C0666E77BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF1ACA-A5C9-4B9A-813A-D6BE3A24BEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="175">
   <si>
     <t>Venue</t>
   </si>
@@ -561,6 +561,9 @@
   </si>
   <si>
     <t>Netwatch Cullen Park, Carlow</t>
+  </si>
+  <si>
+    <t>Pearse Stadium, Salthill</t>
   </si>
 </sst>
 </file>
@@ -932,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -2043,6 +2046,14 @@
         <v>22</v>
       </c>
     </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>174</v>
+      </c>
+      <c r="B139" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDF1ACA-A5C9-4B9A-813A-D6BE3A24BEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3DA1D-3F08-4254-BCC0-F3EBA66C37CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="177">
   <si>
     <t>Venue</t>
   </si>
@@ -564,6 +564,12 @@
   </si>
   <si>
     <t>Pearse Stadium, Salthill</t>
+  </si>
+  <si>
+    <t>TEG Cusack Park, Westmeath</t>
+  </si>
+  <si>
+    <t>Glennon Brother's Pearse Park</t>
   </si>
 </sst>
 </file>
@@ -935,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -2054,6 +2060,22 @@
         <v>88</v>
       </c>
     </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>175</v>
+      </c>
+      <c r="B140" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>176</v>
+      </c>
+      <c r="B141" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/venue_county_list.xlsx
+++ b/venue_county_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmsw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D3DA1D-3F08-4254-BCC0-F3EBA66C37CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016B36EC-1570-40E1-AE43-E037D9D99DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{55CD08A6-343C-4205-AC7E-2A1A947C7589}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="179">
   <si>
     <t>Venue</t>
   </si>
@@ -570,6 +570,12 @@
   </si>
   <si>
     <t>Glennon Brother's Pearse Park</t>
+  </si>
+  <si>
+    <t>MacCumhaill Park, Ballybofey</t>
+  </si>
+  <si>
+    <t>Cedral St Conleth's Park, Newbridge</t>
   </si>
 </sst>
 </file>
@@ -941,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B401E2BE-3312-42BE-8D85-3BE396EF8065}">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
@@ -2076,6 +2082,22 @@
         <v>53</v>
       </c>
     </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>177</v>
+      </c>
+      <c r="B142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>178</v>
+      </c>
+      <c r="B143" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
